--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-04 09:46 UTC · 29 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 45 ms</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9990811.689999999</v>
+        <v>9990955.85</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-5278337.2</v>
+        <v>-1253222.63</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>583.05</v>
+        <v>582.99</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-430.62</v>
+        <v>-73.13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.51</v>
+        <v>-0.26</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1209</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -655,11 +655,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1209</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -678,11 +678,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3369</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -701,11 +701,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3369</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -724,11 +724,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1285</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -940,23 +940,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Port Province</t>
+          <t>National Capital District</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>168000</v>
       </c>
       <c r="E2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="F2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>171309.65</v>
+        <v>171434.2</v>
       </c>
       <c r="I2" t="n">
         <v>1.02</v>
@@ -980,7 +980,7 @@
         <v>0.08</v>
       </c>
       <c r="N2" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="O2" t="n">
         <v>0.0262</v>
@@ -1024,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>136662.19</v>
+        <v>136648.22</v>
       </c>
       <c r="I3" t="n">
         <v>1.04</v>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>61983.85</v>
+        <v>61977.39</v>
       </c>
       <c r="I4" t="n">
         <v>1.02</v>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>55196.57</v>
+        <v>55190.86</v>
       </c>
       <c r="I5" t="n">
         <v>1.02</v>
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>39200.9</v>
+        <v>39196.88</v>
       </c>
       <c r="I6" t="n">
         <v>1.03</v>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>56480.72</v>
+        <v>56475.75</v>
       </c>
       <c r="I7" t="n">
         <v>1.2</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>58991.29</v>
+        <v>58986.85</v>
       </c>
       <c r="I8" t="n">
         <v>1.4</v>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>27713.32</v>
+        <v>27711.31</v>
       </c>
       <c r="I9" t="n">
         <v>1.46</v>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>51107.05</v>
+        <v>51103.02</v>
       </c>
       <c r="I10" t="n">
         <v>1.34</v>
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>124447.26</v>
+        <v>124445.99</v>
       </c>
       <c r="I11" t="n">
         <v>10.37</v>
@@ -1636,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>20860.62</v>
+        <v>20858.92</v>
       </c>
       <c r="I12" t="n">
         <v>1.3</v>
@@ -1704,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>93243.09</v>
+        <v>93236.95</v>
       </c>
       <c r="I13" t="n">
         <v>1.61</v>
@@ -1772,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>32085.79</v>
+        <v>32083.57</v>
       </c>
       <c r="I14" t="n">
         <v>1.53</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>48892.64</v>
+        <v>48889.25</v>
       </c>
       <c r="I15" t="n">
         <v>1.53</v>
@@ -1908,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>27502.11</v>
+        <v>27500.2</v>
       </c>
       <c r="I16" t="n">
         <v>1.53</v>
@@ -1976,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>39228.83</v>
+        <v>39226.28</v>
       </c>
       <c r="I17" t="n">
         <v>1.63</v>
@@ -2044,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>120670.35</v>
+        <v>120669.18</v>
       </c>
       <c r="I18" t="n">
         <v>10.97</v>
@@ -2112,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>70547.48</v>
+        <v>70542.82000000001</v>
       </c>
       <c r="I19" t="n">
         <v>1.6</v>
@@ -2180,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>60329.69</v>
+        <v>60325.56</v>
       </c>
       <c r="I20" t="n">
         <v>1.55</v>
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>43313.62</v>
+        <v>43310.66</v>
       </c>
       <c r="I21" t="n">
         <v>1.55</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>47954.37</v>
+        <v>47951.09</v>
       </c>
       <c r="I22" t="n">
         <v>1.55</v>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>95081.22</v>
+        <v>95080.27</v>
       </c>
       <c r="I23" t="n">
         <v>10.56</v>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>89798.92999999999</v>
+        <v>89798.03</v>
       </c>
       <c r="I24" t="n">
         <v>10.56</v>
@@ -2520,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>11601.86</v>
+        <v>11601.07</v>
       </c>
       <c r="I25" t="n">
         <v>1.55</v>
@@ -2588,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>92740.74000000001</v>
+        <v>92734.17999999999</v>
       </c>
       <c r="I26" t="n">
         <v>1.5</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Losuia Province</t>
+          <t>Milne Bay</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2656,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>95763.64</v>
+        <v>95760.57000000001</v>
       </c>
       <c r="I27" t="n">
         <v>3.3</v>
@@ -2724,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>69346.08</v>
+        <v>69343.86</v>
       </c>
       <c r="I28" t="n">
         <v>3.3</v>
@@ -2792,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>79252.66</v>
+        <v>79250.12</v>
       </c>
       <c r="I29" t="n">
         <v>3.3</v>
@@ -2860,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>46230.72</v>
+        <v>46229.24</v>
       </c>
       <c r="I30" t="n">
         <v>3.3</v>
@@ -2928,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>25428.91</v>
+        <v>25427.11</v>
       </c>
       <c r="I31" t="n">
         <v>1.5</v>
@@ -2996,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>49532.92</v>
+        <v>49531.33</v>
       </c>
       <c r="I32" t="n">
         <v>3.3</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>120539.2</v>
+        <v>120531.68</v>
       </c>
       <c r="I33" t="n">
         <v>1.7</v>
@@ -3132,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>37350.17</v>
+        <v>37347.85</v>
       </c>
       <c r="I34" t="n">
         <v>1.7</v>
@@ -3200,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>22070.56</v>
+        <v>22069.18</v>
       </c>
       <c r="I35" t="n">
         <v>1.7</v>
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>107498.06</v>
+        <v>107497</v>
       </c>
       <c r="I36" t="n">
         <v>10.75</v>
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>18675.09</v>
+        <v>18673.92</v>
       </c>
       <c r="I37" t="n">
         <v>1.7</v>
@@ -3404,7 +3404,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>23768.29</v>
+        <v>23766.81</v>
       </c>
       <c r="I38" t="n">
         <v>1.7</v>
@@ -3456,23 +3456,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Angau Province</t>
+          <t>Morobe</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>188000</v>
       </c>
       <c r="E39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="F39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>224038.4</v>
+        <v>224603.08</v>
       </c>
       <c r="I39" t="n">
         <v>1.19</v>
@@ -3496,7 +3496,7 @@
         <v>0.08</v>
       </c>
       <c r="N39" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
       <c r="O39" t="n">
         <v>0.0252</v>
@@ -3540,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>74873.23</v>
+        <v>74867.52</v>
       </c>
       <c r="I40" t="n">
         <v>1.39</v>
@@ -3608,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>45262.37</v>
+        <v>45259.09</v>
       </c>
       <c r="I41" t="n">
         <v>1.46</v>
@@ -3676,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>69190.33</v>
+        <v>69185.89</v>
       </c>
       <c r="I42" t="n">
         <v>1.65</v>
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>58297.8</v>
+        <v>58293.99</v>
       </c>
       <c r="I43" t="n">
         <v>1.62</v>
@@ -3812,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>196653.58</v>
+        <v>196651.57</v>
       </c>
       <c r="I44" t="n">
         <v>10.35</v>
@@ -3880,7 +3880,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>28005.61</v>
+        <v>28003.81</v>
       </c>
       <c r="I45" t="n">
         <v>1.65</v>
@@ -3948,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>31425.64</v>
+        <v>31423.21</v>
       </c>
       <c r="I46" t="n">
         <v>1.37</v>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Modilon Province</t>
+          <t>Madang</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -4016,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>125346.05</v>
+        <v>125335.89</v>
       </c>
       <c r="I47" t="n">
         <v>1.31</v>
@@ -4084,7 +4084,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>72265.60000000001</v>
+        <v>72261.25999999999</v>
       </c>
       <c r="I48" t="n">
         <v>1.76</v>
@@ -4152,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>51332.21</v>
+        <v>51329.45</v>
       </c>
       <c r="I49" t="n">
         <v>1.97</v>
@@ -4220,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>41211.57</v>
+        <v>41209.24</v>
       </c>
       <c r="I50" t="n">
         <v>1.87</v>
@@ -4288,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>45025.07</v>
+        <v>45022.11</v>
       </c>
       <c r="I51" t="n">
         <v>1.61</v>
@@ -4356,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>121571.23</v>
+        <v>121569.96</v>
       </c>
       <c r="I52" t="n">
         <v>10.13</v>
@@ -4424,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>154839.63</v>
+        <v>154838.15</v>
       </c>
       <c r="I53" t="n">
         <v>11.06</v>
@@ -4492,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>162922.38</v>
+        <v>162913.06</v>
       </c>
       <c r="I54" t="n">
         <v>1.85</v>
@@ -4560,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>96272.31</v>
+        <v>96266.81</v>
       </c>
       <c r="I55" t="n">
         <v>1.85</v>
@@ -4628,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>81461.19</v>
+        <v>81456.53</v>
       </c>
       <c r="I56" t="n">
         <v>1.85</v>
@@ -4696,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>59792.74</v>
+        <v>59790.2</v>
       </c>
       <c r="I57" t="n">
         <v>2.49</v>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>61095.89</v>
+        <v>61092.4</v>
       </c>
       <c r="I58" t="n">
         <v>1.85</v>
@@ -4832,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>49987.55</v>
+        <v>49984.69</v>
       </c>
       <c r="I59" t="n">
         <v>1.85</v>
@@ -4900,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>37370.46</v>
+        <v>37368.88</v>
       </c>
       <c r="I60" t="n">
         <v>2.49</v>
@@ -4968,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>87015.36</v>
+        <v>87010.39</v>
       </c>
       <c r="I61" t="n">
         <v>1.85</v>
@@ -5036,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>72204.24000000001</v>
+        <v>72200.11</v>
       </c>
       <c r="I62" t="n">
         <v>1.85</v>
@@ -5104,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>44433.38</v>
+        <v>44430.84</v>
       </c>
       <c r="I63" t="n">
         <v>1.85</v>
@@ -5172,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>40730.59</v>
+        <v>40728.27</v>
       </c>
       <c r="I64" t="n">
         <v>1.85</v>
@@ -5240,7 +5240,7 @@
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>224255.43</v>
+        <v>224253.53</v>
       </c>
       <c r="I65" t="n">
         <v>12.46</v>
@@ -5308,7 +5308,7 @@
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>148159.41</v>
+        <v>148158.03</v>
       </c>
       <c r="I66" t="n">
         <v>11.4</v>
@@ -5376,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>137044.99</v>
+        <v>137043.82</v>
       </c>
       <c r="I67" t="n">
         <v>12.46</v>
@@ -5444,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>109994.04</v>
+        <v>109986.27</v>
       </c>
       <c r="I68" t="n">
         <v>1.53</v>
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>69946.78</v>
+        <v>69941.60000000001</v>
       </c>
       <c r="I69" t="n">
         <v>1.46</v>
@@ -5580,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>63030.68</v>
+        <v>63026.59</v>
       </c>
       <c r="I70" t="n">
         <v>1.66</v>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>72964.53999999999</v>
+        <v>72960.12</v>
       </c>
       <c r="I71" t="n">
         <v>1.78</v>
@@ -5716,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>45125.94</v>
+        <v>45122.82</v>
       </c>
       <c r="I72" t="n">
         <v>1.56</v>
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>51405.36</v>
+        <v>51401.91</v>
       </c>
       <c r="I73" t="n">
         <v>1.61</v>
@@ -5852,7 +5852,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>153309.07</v>
+        <v>153300.01</v>
       </c>
       <c r="I74" t="n">
         <v>1.83</v>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>82233.57000000001</v>
+        <v>82228.92999999999</v>
       </c>
       <c r="I75" t="n">
         <v>1.91</v>
@@ -5988,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>57917.29</v>
+        <v>57913.95</v>
       </c>
       <c r="I76" t="n">
         <v>1.87</v>
@@ -6056,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>46760.35</v>
+        <v>46757.44</v>
       </c>
       <c r="I77" t="n">
         <v>1.73</v>
@@ -6124,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>186792.71</v>
+        <v>186790.98</v>
       </c>
       <c r="I78" t="n">
         <v>11.67</v>
@@ -6192,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>121240.08</v>
+        <v>121231.57</v>
       </c>
       <c r="I79" t="n">
         <v>1.53</v>
@@ -6260,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>65376.29</v>
+        <v>65371.54</v>
       </c>
       <c r="I80" t="n">
         <v>1.49</v>
@@ -6328,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>56988.25</v>
+        <v>56984.37</v>
       </c>
       <c r="I81" t="n">
         <v>1.58</v>
@@ -6396,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>64811.48</v>
+        <v>64807.28</v>
       </c>
       <c r="I82" t="n">
         <v>1.66</v>
@@ -6464,7 +6464,7 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>37866.25</v>
+        <v>37863.77</v>
       </c>
       <c r="I83" t="n">
         <v>1.65</v>
@@ -6532,7 +6532,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>42677.09</v>
+        <v>42674.07</v>
       </c>
       <c r="I84" t="n">
         <v>1.52</v>
@@ -6600,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>148117.26</v>
+        <v>148105.18</v>
       </c>
       <c r="I85" t="n">
         <v>1.32</v>
@@ -6668,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>48954.3</v>
+        <v>48950.63</v>
       </c>
       <c r="I86" t="n">
         <v>1.44</v>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>45100.28</v>
+        <v>45096.94</v>
       </c>
       <c r="I87" t="n">
         <v>1.45</v>
@@ -6804,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>30748.47</v>
+        <v>30746.09</v>
       </c>
       <c r="I88" t="n">
         <v>1.4</v>
@@ -6872,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>35619.72</v>
+        <v>35616.91</v>
       </c>
       <c r="I89" t="n">
         <v>1.37</v>
@@ -6940,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>84708.00999999999</v>
+        <v>84701.75999999999</v>
       </c>
       <c r="I90" t="n">
         <v>1.46</v>
@@ -7008,7 +7008,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>59237.43</v>
+        <v>59233.01</v>
       </c>
       <c r="I91" t="n">
         <v>1.44</v>
@@ -7076,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>67347.69</v>
+        <v>67342.63</v>
       </c>
       <c r="I92" t="n">
         <v>1.43</v>
@@ -7144,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>36578.93</v>
+        <v>36576.34</v>
       </c>
       <c r="I93" t="n">
         <v>1.52</v>
@@ -7212,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>191445.4</v>
+        <v>191443.36</v>
       </c>
       <c r="I94" t="n">
         <v>10.08</v>
@@ -7280,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>115758.03</v>
+        <v>115750.05</v>
       </c>
       <c r="I95" t="n">
         <v>1.56</v>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>69403.37</v>
+        <v>69398.41</v>
       </c>
       <c r="I96" t="n">
         <v>1.51</v>
@@ -7416,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>52749.22</v>
+        <v>52745.66</v>
       </c>
       <c r="I97" t="n">
         <v>1.6</v>
@@ -7484,7 +7484,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>215793.54</v>
+        <v>215791.27</v>
       </c>
       <c r="I98" t="n">
         <v>10.28</v>
@@ -7552,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>47032.25</v>
+        <v>47029.13</v>
       </c>
       <c r="I99" t="n">
         <v>1.62</v>
@@ -7620,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>40834.44</v>
+        <v>40831.74</v>
       </c>
       <c r="I100" t="n">
         <v>1.63</v>
@@ -7667,28 +7667,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Goroka Base Hospital</t>
+          <t>Goroka Provincial Hospital</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Goroka Province</t>
+          <t>Eastern Highlands</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>108000</v>
       </c>
       <c r="E101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="F101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>190188.93</v>
+        <v>190115.7</v>
       </c>
       <c r="I101" t="n">
         <v>1.76</v>
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>98545.5</v>
+        <v>98538.92999999999</v>
       </c>
       <c r="I102" t="n">
         <v>1.59</v>
@@ -7824,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>59991.38</v>
+        <v>59987.78</v>
       </c>
       <c r="I103" t="n">
         <v>1.76</v>
@@ -7892,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>59200.11</v>
+        <v>59196.83</v>
       </c>
       <c r="I104" t="n">
         <v>1.91</v>
@@ -7960,7 +7960,7 @@
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>49682.16</v>
+        <v>49679.2</v>
       </c>
       <c r="I105" t="n">
         <v>1.77</v>
@@ -8028,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>139747.48</v>
+        <v>139746.1</v>
       </c>
       <c r="I106" t="n">
         <v>10.75</v>
@@ -8096,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>118247.87</v>
+        <v>118246.7</v>
       </c>
       <c r="I107" t="n">
         <v>10.75</v>
@@ -8164,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>85749.17999999999</v>
+        <v>85745.58</v>
       </c>
       <c r="I108" t="n">
         <v>2.52</v>
@@ -8232,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>22698.31</v>
+        <v>22697.36</v>
       </c>
       <c r="I109" t="n">
         <v>2.52</v>
@@ -8300,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>16393.23</v>
+        <v>16392.54</v>
       </c>
       <c r="I110" t="n">
         <v>2.52</v>
@@ -8368,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>13871.19</v>
+        <v>13870.61</v>
       </c>
       <c r="I111" t="n">
         <v>2.52</v>
@@ -8436,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>12610.17</v>
+        <v>12609.64</v>
       </c>
       <c r="I112" t="n">
         <v>2.52</v>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kavieng Province</t>
+          <t>New Ireland</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -8504,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>113370.82</v>
+        <v>113364.68</v>
       </c>
       <c r="I113" t="n">
         <v>1.95</v>
@@ -8572,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>89914.78999999999</v>
+        <v>89909.92</v>
       </c>
       <c r="I114" t="n">
         <v>1.95</v>
@@ -8640,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>38969.49</v>
+        <v>38967.48</v>
       </c>
       <c r="I115" t="n">
         <v>2.05</v>
@@ -8708,7 +8708,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>33229.38</v>
+        <v>33227.58</v>
       </c>
       <c r="I116" t="n">
         <v>1.95</v>
@@ -8776,7 +8776,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>16408.21</v>
+        <v>16407.36</v>
       </c>
       <c r="I117" t="n">
         <v>2.05</v>
@@ -8844,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>28714.36</v>
+        <v>28712.88</v>
       </c>
       <c r="I118" t="n">
         <v>2.05</v>
@@ -8912,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>135525.48</v>
+        <v>135515.74</v>
       </c>
       <c r="I119" t="n">
         <v>1.47</v>
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>86324.87</v>
+        <v>86318.41</v>
       </c>
       <c r="I120" t="n">
         <v>1.42</v>
@@ -9048,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>56316.38</v>
+        <v>56312.35</v>
       </c>
       <c r="I121" t="n">
         <v>1.48</v>
@@ -9116,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>30504.21</v>
+        <v>30501.99</v>
       </c>
       <c r="I122" t="n">
         <v>1.45</v>
@@ -9184,7 +9184,7 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>48002.49</v>
+        <v>48000.06</v>
       </c>
       <c r="I123" t="n">
         <v>2.09</v>
@@ -9252,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>37567.17</v>
+        <v>37565.26</v>
       </c>
       <c r="I124" t="n">
         <v>2.09</v>
@@ -9320,7 +9320,7 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>144052.7</v>
+        <v>144044.44</v>
       </c>
       <c r="I125" t="n">
         <v>1.85</v>
@@ -9388,7 +9388,7 @@
         <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>59098.54</v>
+        <v>59095.16</v>
       </c>
       <c r="I126" t="n">
         <v>1.85</v>
@@ -9456,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>30802.23</v>
+        <v>30800.54</v>
       </c>
       <c r="I127" t="n">
         <v>1.93</v>
@@ -9524,7 +9524,7 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>75720.00999999999</v>
+        <v>75715.67</v>
       </c>
       <c r="I128" t="n">
         <v>1.85</v>
@@ -9592,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>46203.34</v>
+        <v>46200.8</v>
       </c>
       <c r="I129" t="n">
         <v>1.93</v>
@@ -9660,7 +9660,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>138206.84</v>
+        <v>138199.75</v>
       </c>
       <c r="I130" t="n">
         <v>2.06</v>
@@ -9728,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>107265.01</v>
+        <v>107259.51</v>
       </c>
       <c r="I131" t="n">
         <v>2.06</v>
@@ -9796,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>90762.7</v>
+        <v>90758.03999999999</v>
       </c>
       <c r="I132" t="n">
         <v>2.06</v>
@@ -9864,7 +9864,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>37130.2</v>
+        <v>37128.29</v>
       </c>
       <c r="I133" t="n">
         <v>2.06</v>
@@ -9932,7 +9932,7 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>14439.52</v>
+        <v>14438.78</v>
       </c>
       <c r="I134" t="n">
         <v>2.06</v>
@@ -10000,7 +10000,7 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>33004.62</v>
+        <v>33002.92</v>
       </c>
       <c r="I135" t="n">
         <v>2.06</v>
@@ -10179,7 +10179,7 @@
         <v>2721.52</v>
       </c>
       <c r="I2" t="n">
-        <v>114313.66</v>
+        <v>114313.64</v>
       </c>
       <c r="J2" t="n">
         <v>100.39</v>
@@ -10231,7 +10231,7 @@
         <v>195.25</v>
       </c>
       <c r="I3" t="n">
-        <v>14351.99</v>
+        <v>14351.95</v>
       </c>
       <c r="J3" t="n">
         <v>322.81</v>
@@ -10289,7 +10289,7 @@
         <v>195.25</v>
       </c>
       <c r="I4" t="n">
-        <v>21869.71</v>
+        <v>21869.64</v>
       </c>
       <c r="J4" t="n">
         <v>483.47</v>
@@ -10347,7 +10347,7 @@
         <v>195.25</v>
       </c>
       <c r="I5" t="n">
-        <v>12301.71</v>
+        <v>12301.67</v>
       </c>
       <c r="J5" t="n">
         <v>416.21</v>
@@ -10405,7 +10405,7 @@
         <v>2892.77</v>
       </c>
       <c r="I6" t="n">
-        <v>111381.21</v>
+        <v>111381.19</v>
       </c>
       <c r="J6" t="n">
         <v>255.89</v>
@@ -10457,7 +10457,7 @@
         <v>216.81</v>
       </c>
       <c r="I7" t="n">
-        <v>33390.95</v>
+        <v>33390.86</v>
       </c>
       <c r="J7" t="n">
         <v>538.08</v>
@@ -10515,7 +10515,7 @@
         <v>200.68</v>
       </c>
       <c r="I8" t="n">
-        <v>27395.49</v>
+        <v>27395.41</v>
       </c>
       <c r="J8" t="n">
         <v>1162.1</v>
@@ -10573,7 +10573,7 @@
         <v>200.68</v>
       </c>
       <c r="I9" t="n">
-        <v>19668.56</v>
+        <v>19668.5</v>
       </c>
       <c r="J9" t="n">
         <v>1251.46</v>
@@ -10631,7 +10631,7 @@
         <v>200.68</v>
       </c>
       <c r="I10" t="n">
-        <v>21775.9</v>
+        <v>21775.84</v>
       </c>
       <c r="J10" t="n">
         <v>767.52</v>
@@ -10689,7 +10689,7 @@
         <v>200.68</v>
       </c>
       <c r="I11" t="n">
-        <v>5268.36</v>
+        <v>5268.35</v>
       </c>
       <c r="J11" t="n">
         <v>955.4400000000001</v>
@@ -10747,7 +10747,7 @@
         <v>2776.94</v>
       </c>
       <c r="I12" t="n">
-        <v>87481.02</v>
+        <v>87481</v>
       </c>
       <c r="J12" t="n">
         <v>617.75</v>
@@ -10799,7 +10799,7 @@
         <v>2776.94</v>
       </c>
       <c r="I13" t="n">
-        <v>82620.96000000001</v>
+        <v>82620.95</v>
       </c>
       <c r="J13" t="n">
         <v>684.9400000000001</v>
@@ -10851,7 +10851,7 @@
         <v>186.08</v>
       </c>
       <c r="I14" t="n">
-        <v>40383.81</v>
+        <v>40383.69</v>
       </c>
       <c r="J14" t="n">
         <v>448.61</v>
@@ -10909,7 +10909,7 @@
         <v>186.08</v>
       </c>
       <c r="I15" t="n">
-        <v>11072.98</v>
+        <v>11072.95</v>
       </c>
       <c r="J15" t="n">
         <v>358.09</v>
@@ -10967,7 +10967,7 @@
         <v>702.15</v>
       </c>
       <c r="I16" t="n">
-        <v>71274.10000000001</v>
+        <v>71274.05</v>
       </c>
       <c r="J16" t="n">
         <v>534.23</v>
@@ -11025,7 +11025,7 @@
         <v>702.15</v>
       </c>
       <c r="I17" t="n">
-        <v>51612.28</v>
+        <v>51612.24</v>
       </c>
       <c r="J17" t="n">
         <v>758.5700000000001</v>
@@ -11083,7 +11083,7 @@
         <v>702.15</v>
       </c>
       <c r="I18" t="n">
-        <v>58985.47</v>
+        <v>58985.42</v>
       </c>
       <c r="J18" t="n">
         <v>483.91</v>
@@ -11141,7 +11141,7 @@
         <v>702.15</v>
       </c>
       <c r="I19" t="n">
-        <v>34408.19</v>
+        <v>34408.16</v>
       </c>
       <c r="J19" t="n">
         <v>488.03</v>
@@ -11199,7 +11199,7 @@
         <v>702.15</v>
       </c>
       <c r="I20" t="n">
-        <v>36865.92</v>
+        <v>36865.89</v>
       </c>
       <c r="J20" t="n">
         <v>407.1</v>
@@ -11257,7 +11257,7 @@
         <v>243.77</v>
       </c>
       <c r="I21" t="n">
-        <v>60582.07</v>
+        <v>60581.93</v>
       </c>
       <c r="J21" t="n">
         <v>323.36</v>
@@ -11315,7 +11315,7 @@
         <v>243.77</v>
       </c>
       <c r="I22" t="n">
-        <v>18771.91</v>
+        <v>18771.86</v>
       </c>
       <c r="J22" t="n">
         <v>308.79</v>
@@ -11373,7 +11373,7 @@
         <v>243.77</v>
       </c>
       <c r="I23" t="n">
-        <v>11092.49</v>
+        <v>11092.47</v>
       </c>
       <c r="J23" t="n">
         <v>447.3</v>
@@ -11431,7 +11431,7 @@
         <v>243.77</v>
       </c>
       <c r="I24" t="n">
-        <v>9385.950000000001</v>
+        <v>9385.93</v>
       </c>
       <c r="J24" t="n">
         <v>459</v>
@@ -11489,7 +11489,7 @@
         <v>243.77</v>
       </c>
       <c r="I25" t="n">
-        <v>11945.76</v>
+        <v>11945.73</v>
       </c>
       <c r="J25" t="n">
         <v>306.91</v>
@@ -11547,7 +11547,7 @@
         <v>2829.85</v>
       </c>
       <c r="I26" t="n">
-        <v>99053.39999999999</v>
+        <v>99053.38</v>
       </c>
       <c r="J26" t="n">
         <v>315.98</v>
@@ -11599,7 +11599,7 @@
         <v>229.39</v>
       </c>
       <c r="I27" t="n">
-        <v>33722.74</v>
+        <v>33722.65</v>
       </c>
       <c r="J27" t="n">
         <v>117.11</v>
@@ -11657,7 +11657,7 @@
         <v>229.39</v>
       </c>
       <c r="I28" t="n">
-        <v>13649.68</v>
+        <v>13649.65</v>
       </c>
       <c r="J28" t="n">
         <v>106.12</v>
@@ -11715,7 +11715,7 @@
         <v>2715.69</v>
       </c>
       <c r="I29" t="n">
-        <v>180608.72</v>
+        <v>180608.68</v>
       </c>
       <c r="J29" t="n">
         <v>64.55</v>
@@ -11767,7 +11767,7 @@
         <v>322.79</v>
       </c>
       <c r="I30" t="n">
-        <v>29376.07</v>
+        <v>29376.02</v>
       </c>
       <c r="J30" t="n">
         <v>106.06</v>
@@ -11825,7 +11825,7 @@
         <v>293.91</v>
       </c>
       <c r="I31" t="n">
-        <v>22633.3</v>
+        <v>22633.26</v>
       </c>
       <c r="J31" t="n">
         <v>80.93000000000001</v>
@@ -11883,7 +11883,7 @@
         <v>2653.05</v>
       </c>
       <c r="I32" t="n">
-        <v>111437.63</v>
+        <v>111437.6</v>
       </c>
       <c r="J32" t="n">
         <v>98.78</v>
@@ -11935,7 +11935,7 @@
         <v>2918.47</v>
       </c>
       <c r="I33" t="n">
-        <v>143017.1</v>
+        <v>143017.07</v>
       </c>
       <c r="J33" t="n">
         <v>139.33</v>
@@ -11987,7 +11987,7 @@
         <v>287.67</v>
       </c>
       <c r="I34" t="n">
-        <v>88609.32000000001</v>
+        <v>88609.14</v>
       </c>
       <c r="J34" t="n">
         <v>364.01</v>
@@ -12045,7 +12045,7 @@
         <v>287.67</v>
       </c>
       <c r="I35" t="n">
-        <v>52360.05</v>
+        <v>52359.95</v>
       </c>
       <c r="J35" t="n">
         <v>428.56</v>
@@ -12103,7 +12103,7 @@
         <v>287.67</v>
       </c>
       <c r="I36" t="n">
-        <v>44304.66</v>
+        <v>44304.57</v>
       </c>
       <c r="J36" t="n">
         <v>280.66</v>
@@ -12161,7 +12161,7 @@
         <v>287.67</v>
       </c>
       <c r="I37" t="n">
-        <v>33228.49</v>
+        <v>33228.43</v>
       </c>
       <c r="J37" t="n">
         <v>390.59</v>
@@ -12219,7 +12219,7 @@
         <v>287.67</v>
       </c>
       <c r="I38" t="n">
-        <v>27186.95</v>
+        <v>27186.9</v>
       </c>
       <c r="J38" t="n">
         <v>405.44</v>
@@ -12277,7 +12277,7 @@
         <v>287.67</v>
       </c>
       <c r="I39" t="n">
-        <v>47325.43</v>
+        <v>47325.34</v>
       </c>
       <c r="J39" t="n">
         <v>698.29</v>
@@ -12335,7 +12335,7 @@
         <v>287.67</v>
       </c>
       <c r="I40" t="n">
-        <v>39270.04</v>
+        <v>39269.96</v>
       </c>
       <c r="J40" t="n">
         <v>544.61</v>
@@ -12393,7 +12393,7 @@
         <v>287.67</v>
       </c>
       <c r="I41" t="n">
-        <v>24166.18</v>
+        <v>24166.13</v>
       </c>
       <c r="J41" t="n">
         <v>560.1</v>
@@ -12451,7 +12451,7 @@
         <v>287.67</v>
       </c>
       <c r="I42" t="n">
-        <v>22152.33</v>
+        <v>22152.29</v>
       </c>
       <c r="J42" t="n">
         <v>494.37</v>
@@ -12509,7 +12509,7 @@
         <v>470.5</v>
       </c>
       <c r="I43" t="n">
-        <v>39525.54</v>
+        <v>39525.49</v>
       </c>
       <c r="J43" t="n">
         <v>532.85</v>
@@ -12567,7 +12567,7 @@
         <v>470.5</v>
       </c>
       <c r="I44" t="n">
-        <v>24703.46</v>
+        <v>24703.43</v>
       </c>
       <c r="J44" t="n">
         <v>426.83</v>
@@ -12625,7 +12625,7 @@
         <v>3318.05</v>
       </c>
       <c r="I45" t="n">
-        <v>209055.03</v>
+        <v>209055</v>
       </c>
       <c r="J45" t="n">
         <v>460.47</v>
@@ -12677,7 +12677,7 @@
         <v>3014.72</v>
       </c>
       <c r="I46" t="n">
-        <v>137181.34</v>
+        <v>137181.31</v>
       </c>
       <c r="J46" t="n">
         <v>538.6799999999999</v>
@@ -12729,7 +12729,7 @@
         <v>3318.05</v>
       </c>
       <c r="I47" t="n">
-        <v>127755.85</v>
+        <v>127755.83</v>
       </c>
       <c r="J47" t="n">
         <v>395.68</v>
@@ -12781,7 +12781,7 @@
         <v>3094.04</v>
       </c>
       <c r="I48" t="n">
-        <v>173281.24</v>
+        <v>173281.18</v>
       </c>
       <c r="J48" t="n">
         <v>201.21</v>
@@ -12830,10 +12830,10 @@
         <v>66.5057</v>
       </c>
       <c r="H49" t="n">
-        <v>2637.38</v>
+        <v>2637.37</v>
       </c>
       <c r="I49" t="n">
-        <v>175400.54</v>
+        <v>175400.46</v>
       </c>
       <c r="J49" t="n">
         <v>53.72</v>
@@ -12885,7 +12885,7 @@
         <v>2694.46</v>
       </c>
       <c r="I50" t="n">
-        <v>198059.74</v>
+        <v>198059.65</v>
       </c>
       <c r="J50" t="n">
         <v>94.98999999999999</v>
@@ -12937,7 +12937,7 @@
         <v>2829.85</v>
       </c>
       <c r="I51" t="n">
-        <v>128769.41</v>
+        <v>128769.39</v>
       </c>
       <c r="J51" t="n">
         <v>120.54</v>
@@ -12989,7 +12989,7 @@
         <v>2829.85</v>
       </c>
       <c r="I52" t="n">
-        <v>108958.74</v>
+        <v>108958.71</v>
       </c>
       <c r="J52" t="n">
         <v>130.5</v>
@@ -13041,7 +13041,7 @@
         <v>479.26</v>
       </c>
       <c r="I53" t="n">
-        <v>57037.32</v>
+        <v>57037.25</v>
       </c>
       <c r="J53" t="n">
         <v>477.86</v>
@@ -13099,7 +13099,7 @@
         <v>479.26</v>
       </c>
       <c r="I54" t="n">
-        <v>15098.11</v>
+        <v>15098.1</v>
       </c>
       <c r="J54" t="n">
         <v>482.12</v>
@@ -13157,7 +13157,7 @@
         <v>479.26</v>
       </c>
       <c r="I55" t="n">
-        <v>10904.19</v>
+        <v>10904.18</v>
       </c>
       <c r="J55" t="n">
         <v>480.24</v>
@@ -13215,7 +13215,7 @@
         <v>479.26</v>
       </c>
       <c r="I56" t="n">
-        <v>9226.620000000001</v>
+        <v>9226.610000000001</v>
       </c>
       <c r="J56" t="n">
         <v>481.26</v>
@@ -13273,7 +13273,7 @@
         <v>479.26</v>
       </c>
       <c r="I57" t="n">
-        <v>8387.84</v>
+        <v>8387.83</v>
       </c>
       <c r="J57" t="n">
         <v>412.79</v>
@@ -13331,7 +13331,7 @@
         <v>317.17</v>
       </c>
       <c r="I58" t="n">
-        <v>64391.76</v>
+        <v>64391.64</v>
       </c>
       <c r="J58" t="n">
         <v>311.37</v>
@@ -13389,7 +13389,7 @@
         <v>317.17</v>
       </c>
       <c r="I59" t="n">
-        <v>51069.33</v>
+        <v>51069.23</v>
       </c>
       <c r="J59" t="n">
         <v>94.95999999999999</v>
@@ -13447,7 +13447,7 @@
         <v>344.7</v>
       </c>
       <c r="I60" t="n">
-        <v>22924.63</v>
+        <v>22924.59</v>
       </c>
       <c r="J60" t="n">
         <v>182.8</v>
@@ -13505,7 +13505,7 @@
         <v>317.17</v>
       </c>
       <c r="I61" t="n">
-        <v>18873.45</v>
+        <v>18873.41</v>
       </c>
       <c r="J61" t="n">
         <v>175.95</v>
@@ -13563,7 +13563,7 @@
         <v>344.7</v>
       </c>
       <c r="I62" t="n">
-        <v>9652.469999999999</v>
+        <v>9652.459999999999</v>
       </c>
       <c r="J62" t="n">
         <v>205.12</v>
@@ -13621,7 +13621,7 @@
         <v>344.7</v>
       </c>
       <c r="I63" t="n">
-        <v>16891.83</v>
+        <v>16891.8</v>
       </c>
       <c r="J63" t="n">
         <v>368.78</v>
@@ -13679,7 +13679,7 @@
         <v>355</v>
       </c>
       <c r="I64" t="n">
-        <v>28579.76</v>
+        <v>28579.72</v>
       </c>
       <c r="J64" t="n">
         <v>240.83</v>
@@ -13737,7 +13737,7 @@
         <v>355</v>
       </c>
       <c r="I65" t="n">
-        <v>22366.77</v>
+        <v>22366.73</v>
       </c>
       <c r="J65" t="n">
         <v>189.94</v>
@@ -13795,7 +13795,7 @@
         <v>286.36</v>
       </c>
       <c r="I66" t="n">
-        <v>78184.3</v>
+        <v>78184.14999999999</v>
       </c>
       <c r="J66" t="n">
         <v>328.7</v>
@@ -13853,7 +13853,7 @@
         <v>286.36</v>
       </c>
       <c r="I67" t="n">
-        <v>32075.61</v>
+        <v>32075.55</v>
       </c>
       <c r="J67" t="n">
         <v>328.88</v>
@@ -13911,7 +13911,7 @@
         <v>308.74</v>
       </c>
       <c r="I68" t="n">
-        <v>17290.76</v>
+        <v>17290.73</v>
       </c>
       <c r="J68" t="n">
         <v>369.95</v>
@@ -13969,7 +13969,7 @@
         <v>286.36</v>
       </c>
       <c r="I69" t="n">
-        <v>41096.88</v>
+        <v>41096.8</v>
       </c>
       <c r="J69" t="n">
         <v>215.37</v>
@@ -14027,7 +14027,7 @@
         <v>308.74</v>
       </c>
       <c r="I70" t="n">
-        <v>25936.15</v>
+        <v>25936.1</v>
       </c>
       <c r="J70" t="n">
         <v>445.5</v>
@@ -14085,7 +14085,7 @@
         <v>348.06</v>
       </c>
       <c r="I71" t="n">
-        <v>81627.58</v>
+        <v>81627.44</v>
       </c>
       <c r="J71" t="n">
         <v>357.34</v>
@@ -14143,7 +14143,7 @@
         <v>348.06</v>
       </c>
       <c r="I72" t="n">
-        <v>63352.75</v>
+        <v>63352.64</v>
       </c>
       <c r="J72" t="n">
         <v>513.78</v>
@@ -14201,7 +14201,7 @@
         <v>348.06</v>
       </c>
       <c r="I73" t="n">
-        <v>53606.17</v>
+        <v>53606.08</v>
       </c>
       <c r="J73" t="n">
         <v>577.77</v>
@@ -14259,7 +14259,7 @@
         <v>348.06</v>
       </c>
       <c r="I74" t="n">
-        <v>21929.8</v>
+        <v>21929.76</v>
       </c>
       <c r="J74" t="n">
         <v>447.68</v>
@@ -14317,7 +14317,7 @@
         <v>348.06</v>
       </c>
       <c r="I75" t="n">
-        <v>8528.25</v>
+        <v>8528.24</v>
       </c>
       <c r="J75" t="n">
         <v>267.72</v>
@@ -14375,7 +14375,7 @@
         <v>348.06</v>
       </c>
       <c r="I76" t="n">
-        <v>19493.15</v>
+        <v>19493.12</v>
       </c>
       <c r="J76" t="n">
         <v>370.08</v>
@@ -14427,13 +14427,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>587.5544</v>
+        <v>588.0504</v>
       </c>
       <c r="H77" t="n">
-        <v>50.31</v>
+        <v>50.3</v>
       </c>
       <c r="I77" t="n">
-        <v>29558.92</v>
+        <v>29581.26</v>
       </c>
       <c r="J77" t="n">
         <v>4.28</v>
@@ -14485,7 +14485,7 @@
         <v>54.52</v>
       </c>
       <c r="I78" t="n">
-        <v>25192.6</v>
+        <v>25192.34</v>
       </c>
       <c r="J78" t="n">
         <v>13.54</v>
@@ -14537,7 +14537,7 @@
         <v>49.04</v>
       </c>
       <c r="I79" t="n">
-        <v>10471.38</v>
+        <v>10471.26</v>
       </c>
       <c r="J79" t="n">
         <v>1.51</v>
@@ -14589,7 +14589,7 @@
         <v>50.76</v>
       </c>
       <c r="I80" t="n">
-        <v>9595.370000000001</v>
+        <v>9595.27</v>
       </c>
       <c r="J80" t="n">
         <v>5.29</v>
@@ -14641,7 +14641,7 @@
         <v>53.46</v>
       </c>
       <c r="I81" t="n">
-        <v>7111.17</v>
+        <v>7111.1</v>
       </c>
       <c r="J81" t="n">
         <v>11.21</v>
@@ -14693,7 +14693,7 @@
         <v>102.06</v>
       </c>
       <c r="I82" t="n">
-        <v>16790.79</v>
+        <v>16790.7</v>
       </c>
       <c r="J82" t="n">
         <v>103.3</v>
@@ -14745,7 +14745,7 @@
         <v>160.01</v>
       </c>
       <c r="I83" t="n">
-        <v>23523.7</v>
+        <v>23523.61</v>
       </c>
       <c r="J83" t="n">
         <v>171.76</v>
@@ -14797,7 +14797,7 @@
         <v>175.45</v>
       </c>
       <c r="I84" t="n">
-        <v>11668.45</v>
+        <v>11668.42</v>
       </c>
       <c r="J84" t="n">
         <v>218.82</v>
@@ -14846,10 +14846,10 @@
         <v>133.0114</v>
       </c>
       <c r="H85" t="n">
-        <v>142.98</v>
+        <v>142.97</v>
       </c>
       <c r="I85" t="n">
-        <v>19017.32</v>
+        <v>19017.24</v>
       </c>
       <c r="J85" t="n">
         <v>183.69</v>
@@ -14901,7 +14901,7 @@
         <v>131.22</v>
       </c>
       <c r="I86" t="n">
-        <v>7349.15</v>
+        <v>7349.12</v>
       </c>
       <c r="J86" t="n">
         <v>125.96</v>
@@ -14953,7 +14953,7 @@
         <v>218.03</v>
       </c>
       <c r="I87" t="n">
-        <v>44264.03</v>
+        <v>44263.92</v>
       </c>
       <c r="J87" t="n">
         <v>331.17</v>
@@ -15005,7 +15005,7 @@
         <v>225.71</v>
       </c>
       <c r="I88" t="n">
-        <v>18961.63</v>
+        <v>18961.58</v>
       </c>
       <c r="J88" t="n">
         <v>276.29</v>
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>656.3203999999999</v>
+        <v>658.0564000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>100.1</v>
+        <v>100.09</v>
       </c>
       <c r="I89" t="n">
-        <v>65697.49000000001</v>
+        <v>65862.88</v>
       </c>
       <c r="J89" t="n">
         <v>1.06</v>
@@ -15106,10 +15106,10 @@
         <v>189.0162</v>
       </c>
       <c r="H90" t="n">
-        <v>154.87</v>
+        <v>154.86</v>
       </c>
       <c r="I90" t="n">
-        <v>29272.04</v>
+        <v>29271.93</v>
       </c>
       <c r="J90" t="n">
         <v>113.39</v>
@@ -15161,7 +15161,7 @@
         <v>175.87</v>
       </c>
       <c r="I91" t="n">
-        <v>19083.91</v>
+        <v>19083.84</v>
       </c>
       <c r="J91" t="n">
         <v>129.6</v>
@@ -15213,7 +15213,7 @@
         <v>221.39</v>
       </c>
       <c r="I92" t="n">
-        <v>27897</v>
+        <v>27896.93</v>
       </c>
       <c r="J92" t="n">
         <v>209.49</v>
@@ -15265,7 +15265,7 @@
         <v>149.09</v>
       </c>
       <c r="I93" t="n">
-        <v>12002.91</v>
+        <v>12002.86</v>
       </c>
       <c r="J93" t="n">
         <v>101.42</v>
@@ -15317,7 +15317,7 @@
         <v>131.77</v>
       </c>
       <c r="I94" t="n">
-        <v>44277.26</v>
+        <v>44277.07</v>
       </c>
       <c r="J94" t="n">
         <v>1.39</v>
@@ -15369,7 +15369,7 @@
         <v>262.29</v>
       </c>
       <c r="I95" t="n">
-        <v>37642.46</v>
+        <v>37642.38</v>
       </c>
       <c r="J95" t="n">
         <v>202.79</v>
@@ -15421,7 +15421,7 @@
         <v>218.14</v>
       </c>
       <c r="I96" t="n">
-        <v>21380.01</v>
+        <v>21379.95</v>
       </c>
       <c r="J96" t="n">
         <v>132.55</v>
@@ -15473,7 +15473,7 @@
         <v>195.19</v>
       </c>
       <c r="I97" t="n">
-        <v>49192.44</v>
+        <v>49192.16</v>
       </c>
       <c r="J97" t="n">
         <v>122.66</v>
@@ -15525,7 +15525,7 @@
         <v>175.06</v>
       </c>
       <c r="I98" t="n">
-        <v>29412.38</v>
+        <v>29412.19</v>
       </c>
       <c r="J98" t="n">
         <v>80.92</v>
@@ -15577,7 +15577,7 @@
         <v>232.62</v>
       </c>
       <c r="I99" t="n">
-        <v>30940.95</v>
+        <v>30940.8</v>
       </c>
       <c r="J99" t="n">
         <v>166.27</v>
@@ -15629,7 +15629,7 @@
         <v>267.16</v>
       </c>
       <c r="I100" t="n">
-        <v>38341.41</v>
+        <v>38341.25</v>
       </c>
       <c r="J100" t="n">
         <v>226.91</v>
@@ -15681,7 +15681,7 @@
         <v>203.3</v>
       </c>
       <c r="I101" t="n">
-        <v>20636.41</v>
+        <v>20636.3</v>
       </c>
       <c r="J101" t="n">
         <v>114.8</v>
@@ -15733,7 +15733,7 @@
         <v>217.68</v>
       </c>
       <c r="I102" t="n">
-        <v>24382.43</v>
+        <v>24382.3</v>
       </c>
       <c r="J102" t="n">
         <v>140.05</v>
@@ -15785,7 +15785,7 @@
         <v>280.16</v>
       </c>
       <c r="I103" t="n">
-        <v>82373.87</v>
+        <v>82373.53999999999</v>
       </c>
       <c r="J103" t="n">
         <v>249.72</v>
@@ -15837,7 +15837,7 @@
         <v>305.1</v>
       </c>
       <c r="I104" t="n">
-        <v>45921.51</v>
+        <v>45921.34</v>
       </c>
       <c r="J104" t="n">
         <v>293.5</v>
@@ -15889,7 +15889,7 @@
         <v>292.5</v>
       </c>
       <c r="I105" t="n">
-        <v>31738.82</v>
+        <v>31738.7</v>
       </c>
       <c r="J105" t="n">
         <v>271.38</v>
@@ -15941,7 +15941,7 @@
         <v>253.52</v>
       </c>
       <c r="I106" t="n">
-        <v>23959.75</v>
+        <v>23959.65</v>
       </c>
       <c r="J106" t="n">
         <v>202.96</v>
@@ -15993,7 +15993,7 @@
         <v>197.19</v>
       </c>
       <c r="I107" t="n">
-        <v>54527.22</v>
+        <v>54526.91</v>
       </c>
       <c r="J107" t="n">
         <v>126.8</v>
@@ -16045,7 +16045,7 @@
         <v>183.23</v>
       </c>
       <c r="I108" t="n">
-        <v>28219.75</v>
+        <v>28219.58</v>
       </c>
       <c r="J108" t="n">
         <v>97.86</v>
@@ -16097,7 +16097,7 @@
         <v>210.99</v>
       </c>
       <c r="I109" t="n">
-        <v>26587.45</v>
+        <v>26587.31</v>
       </c>
       <c r="J109" t="n">
         <v>128.31</v>
@@ -16149,7 +16149,7 @@
         <v>233.51</v>
       </c>
       <c r="I110" t="n">
-        <v>31877.29</v>
+        <v>31877.13</v>
       </c>
       <c r="J110" t="n">
         <v>167.84</v>
@@ -16201,7 +16201,7 @@
         <v>229.09</v>
       </c>
       <c r="I111" t="n">
-        <v>18443.52</v>
+        <v>18443.43</v>
       </c>
       <c r="J111" t="n">
         <v>160.08</v>
@@ -16253,7 +16253,7 @@
         <v>194.19</v>
       </c>
       <c r="I112" t="n">
-        <v>19032.02</v>
+        <v>19031.91</v>
       </c>
       <c r="J112" t="n">
         <v>98.81</v>
@@ -16305,7 +16305,7 @@
         <v>136.56</v>
       </c>
       <c r="I113" t="n">
-        <v>53537</v>
+        <v>53536.56</v>
       </c>
       <c r="J113" t="n">
         <v>2.42</v>
@@ -16357,7 +16357,7 @@
         <v>170.09</v>
       </c>
       <c r="I114" t="n">
-        <v>20242.43</v>
+        <v>20242.3</v>
       </c>
       <c r="J114" t="n">
         <v>56.51</v>
@@ -16409,7 +16409,7 @@
         <v>174.38</v>
       </c>
       <c r="I115" t="n">
-        <v>18921.81</v>
+        <v>18921.69</v>
       </c>
       <c r="J115" t="n">
         <v>64.04000000000001</v>
@@ -16461,7 +16461,7 @@
         <v>158.04</v>
       </c>
       <c r="I116" t="n">
-        <v>12170.2</v>
+        <v>12170.11</v>
       </c>
       <c r="J116" t="n">
         <v>35.36</v>
@@ -16513,7 +16513,7 @@
         <v>150.14</v>
       </c>
       <c r="I117" t="n">
-        <v>13663.59</v>
+        <v>13663.48</v>
       </c>
       <c r="J117" t="n">
         <v>29.25</v>
@@ -16565,7 +16565,7 @@
         <v>175.99</v>
       </c>
       <c r="I118" t="n">
-        <v>35728.95</v>
+        <v>35728.72</v>
       </c>
       <c r="J118" t="n">
         <v>82.84999999999999</v>
@@ -16617,7 +16617,7 @@
         <v>171.51</v>
       </c>
       <c r="I119" t="n">
-        <v>24614.3</v>
+        <v>24614.14</v>
       </c>
       <c r="J119" t="n">
         <v>73.56999999999999</v>
@@ -16669,7 +16669,7 @@
         <v>168.12</v>
       </c>
       <c r="I120" t="n">
-        <v>27657.76</v>
+        <v>27657.58</v>
       </c>
       <c r="J120" t="n">
         <v>66.53</v>
@@ -16721,7 +16721,7 @@
         <v>194.17</v>
       </c>
       <c r="I121" t="n">
-        <v>16311.73</v>
+        <v>16311.63</v>
       </c>
       <c r="J121" t="n">
         <v>98.78</v>
@@ -16773,7 +16773,7 @@
         <v>205.65</v>
       </c>
       <c r="I122" t="n">
-        <v>53267.5</v>
+        <v>53267.21</v>
       </c>
       <c r="J122" t="n">
         <v>144.34</v>
@@ -16825,7 +16825,7 @@
         <v>189.78</v>
       </c>
       <c r="I123" t="n">
-        <v>30557.91</v>
+        <v>30557.72</v>
       </c>
       <c r="J123" t="n">
         <v>111.45</v>
@@ -16877,7 +16877,7 @@
         <v>215.41</v>
       </c>
       <c r="I124" t="n">
-        <v>24881.82</v>
+        <v>24881.69</v>
       </c>
       <c r="J124" t="n">
         <v>136.06</v>
@@ -16929,7 +16929,7 @@
         <v>222.08</v>
       </c>
       <c r="I125" t="n">
-        <v>22542.72</v>
+        <v>22542.61</v>
       </c>
       <c r="J125" t="n">
         <v>178.4</v>
@@ -16981,7 +16981,7 @@
         <v>225.38</v>
       </c>
       <c r="I126" t="n">
-        <v>19722.77</v>
+        <v>19722.67</v>
       </c>
       <c r="J126" t="n">
         <v>153.57</v>
@@ -17027,13 +17027,13 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>378.1564</v>
+        <v>378.0324</v>
       </c>
       <c r="H127" t="n">
         <v>261.68</v>
       </c>
       <c r="I127" t="n">
-        <v>98956.61</v>
+        <v>98924.52</v>
       </c>
       <c r="J127" t="n">
         <v>334.85</v>
@@ -17085,7 +17085,7 @@
         <v>212.83</v>
       </c>
       <c r="I128" t="n">
-        <v>46188.57</v>
+        <v>46188.44</v>
       </c>
       <c r="J128" t="n">
         <v>233.57</v>
@@ -17137,7 +17137,7 @@
         <v>262.83</v>
       </c>
       <c r="I129" t="n">
-        <v>31279.52</v>
+        <v>31279.45</v>
       </c>
       <c r="J129" t="n">
         <v>282.24</v>
@@ -17189,7 +17189,7 @@
         <v>304.32</v>
       </c>
       <c r="I130" t="n">
-        <v>33021.65</v>
+        <v>33021.59</v>
       </c>
       <c r="J130" t="n">
         <v>355.07</v>
@@ -17241,7 +17241,7 @@
         <v>265.66</v>
       </c>
       <c r="I131" t="n">
-        <v>26037.1</v>
+        <v>26037.04</v>
       </c>
       <c r="J131" t="n">
         <v>287.21</v>
@@ -17290,10 +17290,10 @@
         <v>322.0276</v>
       </c>
       <c r="H132" t="n">
-        <v>179.6</v>
+        <v>179.59</v>
       </c>
       <c r="I132" t="n">
-        <v>57834.55</v>
+        <v>57834.37</v>
       </c>
       <c r="J132" t="n">
         <v>31.5</v>
@@ -17345,7 +17345,7 @@
         <v>163.04</v>
       </c>
       <c r="I133" t="n">
-        <v>34812.4</v>
+        <v>34812.28</v>
       </c>
       <c r="J133" t="n">
         <v>1.35</v>
@@ -17397,7 +17397,7 @@
         <v>182.14</v>
       </c>
       <c r="I134" t="n">
-        <v>24226.65</v>
+        <v>24226.57</v>
       </c>
       <c r="J134" t="n">
         <v>36.5</v>
@@ -17449,7 +17449,7 @@
         <v>173.73</v>
       </c>
       <c r="I135" t="n">
-        <v>12770.41</v>
+        <v>12770.37</v>
       </c>
       <c r="J135" t="n">
         <v>19.98</v>
@@ -17563,16 +17563,16 @@
         <v>1034000</v>
       </c>
       <c r="D5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1257438.51</v>
+        <v>1258055.97</v>
       </c>
       <c r="H5" t="n">
         <v>1.22</v>
@@ -17603,7 +17603,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1451090.34</v>
+        <v>1450991.39</v>
       </c>
       <c r="H6" t="n">
         <v>1.57</v>
@@ -17634,7 +17634,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1579475.14</v>
+        <v>1579368.62</v>
       </c>
       <c r="H7" t="n">
         <v>1.59</v>
@@ -17656,16 +17656,16 @@
         <v>967500</v>
       </c>
       <c r="D8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1807412.88</v>
+        <v>1807248.22</v>
       </c>
       <c r="H8" t="n">
         <v>1.87</v>
@@ -17696,7 +17696,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3895394.82</v>
+        <v>3895291.66</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -17741,7 +17741,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>One-off cost 63,000 PGK · annual change -5,278,337 PGK · payback 0.01 years</t>
+          <t>One-off cost 63,000 PGK · annual change -1,253,223 PGK · payback 0.05 years</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 45 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 40 ms</t>
         </is>
       </c>
     </row>
@@ -798,6 +798,157 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Share of demand volume that is estimated</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Facilities with estimated demand</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>134</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8233869.1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>11655092.35</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 40 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:51 UTC · 57 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:51 UTC · 57 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 44 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 44 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 46 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 46 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:58 UTC · 47 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:58 UTC · 47 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 92 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 92 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 56 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 56 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 80 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 80 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 54 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 54 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 48 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 48 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:15 UTC · 163 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:15 UTC · 163 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 50 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-7.xlsx
+++ b/docs/app/api/files/results-7.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 50 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:14 UTC · 45 ms</t>
         </is>
       </c>
     </row>
